--- a/test/test1b.xlsx
+++ b/test/test1b.xlsx
@@ -10,6 +10,9 @@
     <sheet name="Scenes" sheetId="1" r:id="rId4"/>
     <sheet name="Statistics" sheetId="2" r:id="rId5"/>
     <sheet name="Characters" sheetId="3" r:id="rId6"/>
+    <sheet name="Locations" sheetId="4" r:id="rId7"/>
+    <sheet name="Analysis" sheetId="5" r:id="rId8"/>
+    <sheet name="jane" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -17,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -34,25 +37,41 @@
     <t>Goal</t>
   </si>
   <si>
+    <t>Characters</t>
+  </si>
+  <si>
     <t>Like, Words, man.</t>
   </si>
   <si>
+    <t>Sentence Lengths</t>
+  </si>
+  <si>
     <t>Synopsis</t>
   </si>
   <si>
+    <t>Making a Scene</t>
+  </si>
+  <si>
+    <t>1st Draft</t>
+  </si>
+  <si>
     <t>Earth</t>
   </si>
   <si>
-    <t>Making a Scene</t>
-  </si>
-  <si>
-    <t>1st Draft</t>
-  </si>
-  <si>
     <t>Demonstrate that it’s worth exploring the next scene</t>
   </si>
   <si>
+    <t>John
+Jane</t>
+  </si>
+  <si>
+    <t>16@3.4: P5:4m.s, P6:5m.s, P4:m.l.m.s, P4:3m.s, P6:l.4m.s, P4:m.3s, P3:l.m.s, P2:l.s, P3:l.m.s, P4:3m.s, P2:m.l, P2:2s, P2:2s, P2:2s, P2:m.s, P3:2m.s</t>
+  </si>
+  <si>
     <t>Another Scene</t>
+  </si>
+  <si>
+    <t>2@3: P3:m.l.s, P3:2m.s</t>
   </si>
   <si>
     <t>This is the first bit
@@ -62,13 +81,22 @@
     <t>More Scenes</t>
   </si>
   <si>
+    <t>11@3: P3:2m.s, P3:m.l.s, P3:2m.s, P3:m.l.s, P3:2m.s, P3:m.l.s, P3:2m.s, P3:m.l.s, P3:2m.s, P3:m.l.s, P3:2m.s</t>
+  </si>
+  <si>
     <t>An embedded scene</t>
   </si>
   <si>
+    <t>1@2: P2:m.s</t>
+  </si>
+  <si>
+    <t>Jane Cannot Find John</t>
+  </si>
+  <si>
     <t>Space</t>
   </si>
   <si>
-    <t>Jane Cannot Find John</t>
+    <t>1@3: P3:2m.s</t>
   </si>
   <si>
     <t>We Found John!</t>
@@ -80,12 +108,18 @@
     <t>Mars</t>
   </si>
   <si>
+    <t>1@3: P3:m.l.s</t>
+  </si>
+  <si>
     <t>Scene One</t>
   </si>
   <si>
     <t>3rd Draft</t>
   </si>
   <si>
+    <t>2@3: P3:2m.s, P3:2m.s</t>
+  </si>
+  <si>
     <t>Scenes</t>
   </si>
   <si>
@@ -101,37 +135,142 @@
     <t>Total</t>
   </si>
   <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>The sidekick</t>
+  </si>
+  <si>
+    <t>Jane Smith</t>
+  </si>
+  <si>
+    <t>The heroine</t>
+  </si>
+  <si>
     <t>Tag</t>
   </si>
   <si>
-    <t>Given</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>Pronouns</t>
-  </si>
-  <si>
-    <t>Fate</t>
-  </si>
-  <si>
-    <t>John Smith</t>
-  </si>
-  <si>
-    <t>John | John Smith</t>
-  </si>
-  <si>
-    <t>The sidekick</t>
-  </si>
-  <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
-    <t>Jane | Jane Smith</t>
-  </si>
-  <si>
-    <t>The heroine</t>
+    <t>Location(s)</t>
+  </si>
+  <si>
+    <t>FreemanHome</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Phrase</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>you</t>
+  </si>
+  <si>
+    <t>can</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>this</t>
+  </si>
+  <si>
+    <t>as</t>
+  </si>
+  <si>
+    <t>scene</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>chapter</t>
+  </si>
+  <si>
+    <t>also</t>
+  </si>
+  <si>
+    <t>heading</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>files</t>
+  </si>
+  <si>
+    <t>three</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>adding</t>
+  </si>
+  <si>
+    <t>more</t>
+  </si>
+  <si>
+    <t>scenes</t>
+  </si>
+  <si>
+    <t>be</t>
+  </si>
+  <si>
+    <t>you can</t>
+  </si>
+  <si>
+    <t>in the</t>
+  </si>
+  <si>
+    <t>level three</t>
+  </si>
+  <si>
+    <t>three heading</t>
+  </si>
+  <si>
+    <t>level three heading</t>
+  </si>
+  <si>
+    <t>adding more</t>
+  </si>
+  <si>
+    <t>Scene</t>
   </si>
 </sst>
 </file>
@@ -179,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -197,9 +336,6 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="3" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -501,19 +637,21 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="true" style="0"/>
-    <col min="2" max="2" width="22" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10" customWidth="true" style="0"/>
-    <col min="4" max="4" width="7.2" customWidth="true" style="0"/>
-    <col min="5" max="5" width="55" customWidth="true" style="0"/>
-    <col min="6" max="6" width="24" customWidth="true" style="0"/>
-    <col min="7" max="7" width="23" customWidth="true" style="0"/>
+    <col min="1" max="1" width="2.65" customWidth="true" style="0"/>
+    <col min="2" max="2" width="23.05" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.05" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.22" customWidth="true" style="0"/>
+    <col min="5" max="5" width="53.5" customWidth="true" style="0"/>
+    <col min="6" max="6" width="13.32" customWidth="true" style="0"/>
+    <col min="7" max="7" width="20.94" customWidth="true" style="0"/>
+    <col min="8" max="8" width="120" customWidth="true" style="0"/>
+    <col min="9" max="9" width="20.5" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,158 +673,179 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4">
+        <v>532</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4">
+        <v>79</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4">
+        <v>420</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4">
-        <v>534</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="4">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="4">
-        <v>420</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="4">
-        <v>7</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="4">
-        <v>21</v>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D8" s="5"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="4">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="4">
+      <c r="F8" s="5"/>
+      <c r="G8" s="4">
         <v>51</v>
       </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="F10" s="6">
-        <v>1146</v>
+      <c r="H8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="G9" s="6">
+        <v>1143</v>
       </c>
     </row>
   </sheetData>
@@ -704,15 +863,15 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.6" customWidth="true" style="0"/>
+    <col min="1" max="1" width="10.05" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -720,27 +879,27 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6">
         <v>5</v>
@@ -748,22 +907,22 @@
       <c r="C3" s="6">
         <v>0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>5</v>
       </c>
       <c r="E3" s="6">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F3" s="6">
         <v>0</v>
       </c>
-      <c r="G3" s="7">
-        <v>1061</v>
+      <c r="G3" s="6">
+        <v>1058</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
@@ -771,7 +930,7 @@
       <c r="C4" s="6">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>1</v>
       </c>
       <c r="E4" s="6">
@@ -780,13 +939,13 @@
       <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
@@ -794,7 +953,7 @@
       <c r="C5" s="6">
         <v>0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>1</v>
       </c>
       <c r="E5" s="6">
@@ -803,13 +962,13 @@
       <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B6" s="6">
         <v>7</v>
@@ -817,17 +976,17 @@
       <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>7</v>
       </c>
       <c r="E6" s="6">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="7">
-        <v>1146</v>
+      <c r="G6" s="6">
+        <v>1143</v>
       </c>
     </row>
   </sheetData>
@@ -842,188 +1001,441 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="true" style="0"/>
-    <col min="2" max="2" width="11" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18" customWidth="true" style="0"/>
-    <col min="4" max="4" width="7" customWidth="true" style="0"/>
-    <col min="5" max="5" width="10" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12" customWidth="true" style="0"/>
-    <col min="7" max="7" width="6" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13" customWidth="true" style="0"/>
+    <col min="1" max="1" width="12.1" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.4" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="6.85" customWidth="true" style="0"/>
+    <col min="2" max="2" width="14.95" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.42" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="7.35" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.06" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.95" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.06" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="6">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="6">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="6">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="6">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="6">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="6">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="2.65" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.3" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.08" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
